--- a/healthcare_forms/005_dental_trauma_management_quiz--healthcare_forms.xlsx
+++ b/healthcare_forms/005_dental_trauma_management_quiz--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>trauma_score</t>
+          <t>trauma_score_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>trauma score</t>
+          <t>Trauma Score 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>treatment_plan</t>
+          <t>treatment_plan_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>treatment plan</t>
+          <t>Treatment Plan 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>trauma_assessment</t>
+          <t>trauma_assessment_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>trauma assessment</t>
+          <t>Trauma Assessment 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -849,7 +849,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>trauma_score_choices</t>
+          <t>trauma_score_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -866,7 +866,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>trauma_score_choices</t>
+          <t>trauma_score_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -883,7 +883,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>trauma_score_choices</t>
+          <t>trauma_score_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
